--- a/payment_forms/048_premium_credit_card_application_form--payment_forms.xlsx
+++ b/payment_forms/048_premium_credit_card_application_form--payment_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,8 +1102,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
-    <col width="43" customWidth="1" min="2" max="2"/>
-    <col width="43" customWidth="1" min="3" max="3"/>
+    <col width="21" customWidth="1" min="2" max="2"/>
+    <col width="21" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'employed'}</t>
+          <t>employed</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Employed'}</t>
+          <t>Employed</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'unemployed'}</t>
+          <t>unemployed</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Unemployed'}</t>
+          <t>Unemployed</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'self-employed'}</t>
+          <t>self-employed</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Self-Employed'}</t>
+          <t>Self-Employed</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Student'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'full-time'}</t>
+          <t>full-time</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Full-time'}</t>
+          <t>Full-time</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'part-time'}</t>
+          <t>part-time</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Part-time'}</t>
+          <t>Part-time</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'freelance'}</t>
+          <t>freelance</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Freelance'}</t>
+          <t>Freelance</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'1,000_-_2,000'}</t>
+          <t>1,000_-_2,000</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '1,000 - 2,000'}</t>
+          <t>1,000 - 2,000</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'2,000_-_5,000'}</t>
+          <t>2,000_-_5,000</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '2,000 - 5,000'}</t>
+          <t>2,000 - 5,000</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'5,000_-_8,000'}</t>
+          <t>5,000_-_8,000</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '5,000 - 8,000'}</t>
+          <t>5,000 - 8,000</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'8,000_-_10,000'}</t>
+          <t>8,000_-_10,000</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '8,000 - 10,000'}</t>
+          <t>8,000 - 10,000</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'artist'}</t>
+          <t>artist</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': 'Artist'}</t>
+          <t>Artist</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'doctor'}</t>
+          <t>doctor</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': 'Doctor'}</t>
+          <t>Doctor</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'engineer'}</t>
+          <t>engineer</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Engineer'}</t>
+          <t>Engineer</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'lawyer'}</t>
+          <t>lawyer</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'Lawyer'}</t>
+          <t>Lawyer</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'student'}</t>
+          <t>student</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Student'}</t>
+          <t>Student</t>
         </is>
       </c>
     </row>
@@ -1539,12 +1539,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_"bachelor's_degree"}</t>
+          <t>bachelor's_degree</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': "Bachelor's Degree"}</t>
+          <t>Bachelor's Degree</t>
         </is>
       </c>
     </row>
@@ -1556,12 +1556,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_"master's_degree"}</t>
+          <t>master's_degree</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': "Master's Degree"}</t>
+          <t>Master's Degree</t>
         </is>
       </c>
     </row>
@@ -1573,12 +1573,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'doctoral_degree'}</t>
+          <t>doctoral_degree</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': 'Doctoral Degree'}</t>
+          <t>Doctoral Degree</t>
         </is>
       </c>
     </row>
@@ -1590,12 +1590,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'high_school_diploma'}</t>
+          <t>high_school_diploma</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': 'High School Diploma'}</t>
+          <t>High School Diploma</t>
         </is>
       </c>
     </row>
@@ -1607,12 +1607,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'id':_5,_'label':_'some_high_school'}</t>
+          <t>some_high_school</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'id': 5, 'label': 'Some High School'}</t>
+          <t>Some High School</t>
         </is>
       </c>
     </row>
@@ -1624,12 +1624,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_'600_-_700'}</t>
+          <t>600_-_700</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': '600 - 700'}</t>
+          <t>600 - 700</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_'700_-_800'}</t>
+          <t>700_-_800</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': '700 - 800'}</t>
+          <t>700 - 800</t>
         </is>
       </c>
     </row>
@@ -1658,12 +1658,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'id':_3,_'label':_'800_-_900'}</t>
+          <t>800_-_900</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'id': 3, 'label': '800 - 900'}</t>
+          <t>800 - 900</t>
         </is>
       </c>
     </row>
@@ -1675,12 +1675,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'id':_4,_'label':_'900_-_1000'}</t>
+          <t>900_-_1000</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'id': 4, 'label': '900 - 1000'}</t>
+          <t>900 - 1000</t>
         </is>
       </c>
     </row>
@@ -1692,12 +1692,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'id':_1,_'label':_true}</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'id': 1, 'label': True}</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1709,12 +1709,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'id':_2,_'label':_false}</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'id': 2, 'label': False}</t>
+          <t>False</t>
         </is>
       </c>
     </row>
